--- a/TESTS/zlit_5_khlopchyk_zirka.xlsx
+++ b/TESTS/zlit_5_khlopchyk_zirka.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Оскар Вайльд — видатний ірландський письменник відомий своїми літературними казками</t>
+          <t>Оскар Вайльд</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -645,6 +655,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ірландія — хоча він жив і творив переважно в Лондоні</t>
+          <t>Ірландія</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Дитиною зорі — надзвичайно красивим але гордим жорстоким і зневажливим до бідних і некрасивих</t>
+          <t>Дитиною зорі</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Пихатістю і жорстокістю — він знущався над бідними і потворними бо вважав себе вищим від усіх</t>
+          <t>Пихатістю і жорстокістю</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Бо він з'явився ніби зірка що впала з неба — і виріс надзвичайно красивим немов зіркове дитя</t>
+          <t>Бо він з'явився ніби зірка що впала з неба</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Він відкинув її з огидою і соромом — не хотів визнавати потворну жебрачку матір'ю</t>
+          <t>Він відкинув її з огидою і соромом</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Жорстоко і зневажливо — вигнав її не хотів ганьбити себе зв'язком з жебрачкою</t>
+          <t>Жорстоко і зневажливо</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Він покрився виразками і зробився потворним як жаба — краса зникла разом з добром у серці</t>
+          <t>Він покрився виразками і зробився потворним як жаба</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Як двоє лісорубів знайшли майбутнього хлопчика-зірку?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він сидів під деревом</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Уночі з неба впала зірка, а вранці на тому місці лісоруби знайшли сповите дитя</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його залишили біля хати</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він прийшов сам до села</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що носив на шиї знайдений хлопчик, що вказувало на його незвичне походження?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Срібний хрестик</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Золотий ланцюжок із дорогоцінним каменем</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дзвіночок</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого особливого</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Як один із лісорубів, що знайшов дитину, вирішив із нею вчинити?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишив у лісі</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Попри бідність, узяв додому і виховав як рідного, разом зі своїми дітьми</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Продав багатіям</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Відніс до короля</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Як хлопчик-зірка ставився до інших дітей села, коли підріс?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Дружньо й рівно</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зверхньо — глузував з тих, хто був бідний, кривий чи негарний на вигляд</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Байдуже</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Допомагав їм завжди</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Чим хлопчик-зірка пояснював своє право зневажати інших?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він нічим це не пояснював</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Своєю незвичайною красою — вважав себе вищим за «звичайних» людей</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Своїм багатством</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Своєю силою</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як односельці спочатку ставились до вродливого, але жорстокого хлопчика?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одразу його уникали</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Багато хто все ж тягнувся до нього через красу, попри його злий характер</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ненавиділи відкрито</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не помічали його</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Хто прийшла до села того дня, коли хлопчик-зірка виявив свою найбільшу жорстокість?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Стара чаклунка</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бідна виснажена жебрачка, яка шукала свого зниклого багато років тому сина</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подорожній купець</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Королева</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>За якими ознаками жебрачка впізнала в хлопчику-зірці свого сина?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>За одягом</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>За золотим ланцюжком із каменем на його шиї — тим самим, що був на її дитині</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>За голосом</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>За іменем</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Як саме хлопчик-зірка прогнав жебрачку, коли вона назвала себе його матір'ю?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Мовчки пішов</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Із огидою назвав її брехливою каліцею і жбурнув у неї каменем</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Заплакав і втік</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Покликав на допомогу</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що сталося з обличчям і тілом хлопчика-зірки одразу після того, як він прогнав матір?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не сталось</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дивлячись у воду, він побачив, що став потворним, схожим на жабу</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він посивів</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він став невидимим</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як односельці поставились до хлопчика, коли побачили його новий, потворний вигляд?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Пожаліли його</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Прогнали з села — тепер його зневажали так, як він колись зневажав інших</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Не помітили змін</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Стали йому служити</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що хлопчик-зірка вирішив робити після вигнання з села?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Оселитися в лісі назавжди</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вирушити світом на пошуки матері, щоб попросити пробачення</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Знайти нову красу</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Помститися селянам</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Хто зустрів потворного хлопчика в лісі й узяв його собі на службу?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Добрий чарівник</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Злий і жадібний маг, що жив у лісі</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Король</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Старий лісоруб</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Скільки разів маг наказав хлопчику приносити йому золоті монети з лісу?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Один раз</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тричі, щодня по одній монеті</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>П'ять разів</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Безліч разів без кінця</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що хлопчик-зірка робив щоразу, знаходячи в лісі золоту монету?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишав собі</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зустрічав ще жалюгіднішого жебрака і віддавав монету йому</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Закопував у землю</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Приносив магу одразу дві</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що сталося з хлопчиком після третього разу, коли він віддав монету жебраку?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Маг його покарав ще суворіше</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>До нього повернулась його колишня краса, бо серце нарешті стало добрим</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він залишився потворним назавжди</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він отримав ще одне завдання</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Кого хлопчик-зірка зустрів одразу після того, як до нього повернулася краса?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Чарівника</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Свою справжню матір і батька — короля та королеву, що шукали його</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Стару жебрачку</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Друзів з рідного села</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Яким став хлопчик-зірка після повернення додому як принц?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Таким же гордим, як і раніше</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Справедливим і добрим правителем, що допомагав найбіднішим</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Слабким і хворим</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Самотнім відлюдьком</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>До якої жанрової традиції належить «Хлопчик-Зірка»?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Народна казка без автора</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Авторська літературна казка з глибоким моральним уроком, як у Оскара Вайльда</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Реалістичне оповідання</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Пригодницький роман</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чим закінчується «Хлопчик-Зірка» для головного героя?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він залишається потворним назавжди</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Краса повертається, і він стає справедливим та добрим правителем</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він помирає</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він зникає безвісти</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яку загальну ідею про красу стверджує казка «Хлопчик-Зірка»?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зовнішня краса найважливіша</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Справжня краса — у доброті серця, а не у зовнішності</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Краса не має значення взагалі</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Красиві люди завжди добрі</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що символізує перетворення красивого хлопчика на потворного?</t>
+          <t>Перетворення красивого хлопчика на потворного символізує покарання за гордість і жорстокість серця.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яка євангельська тема відчутна у казці «Хлопчик-Зірка»?</t>
+          <t>У казці «Хлопчик-Зірка» відчутна біблійна тема покаяння і спокути через страждання.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між казками Вайльда і казками Андерсена?</t>
+          <t>Як і Андерсен, Вайльд у своїх казках часто поєднує казковий сюжет із глибоким моральним уроком.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,29 +2207,32 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Коли повернулась краса до хлопчика-зірки?</t>
+          <t>Краса повернулася до хлопчика-зірки одразу, щойно він прогнав свою матір.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яким чином закінчується казка «Хлопчик-Зірка»?</t>
+          <t>Казка «Хлопчик-Зірка» закінчується тим, що герой стає справедливим правителем.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна думка казки «Хлопчик-Зірка»?</t>
+          <t>Головна думка казки — зовнішня краса важливіша за доброту серця.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які пороки головного героя показує казка «Хлопчик-Зірка»?</t>
+          <t>Що допомогло хлопчику-зірці повернути собі справжню красу?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Гордість і пиха</t>
+          <t>Каяття за жорстокість до матері</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Жорстокість до бідних</t>
+          <t>Тричі віддані золоті монети жебракам</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Трудолюбство</t>
+          <t>Заклинання злого мага</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Зневага до матері</t>
+          <t>Доброта серця, що нарешті прокинулась</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Свою матір щоб попросити пробачення — він вирушив у пошуки щоб спокутувати свою провину</t>
+          <t>Свою матір щоб попросити пробачення</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Тричі приносити до нього золоті монети що він знайде в лісі — під загрозою страшної кари</t>
+          <t>Тричі приносити до нього золоті монети що він знайде в лісі</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Щоразу ділився монетою з ще жалюгіднішим жебраком ніж він сам — і кожного разу магія повертала гроші</t>
+          <t>Щоразу ділився монетою з ще жалюгіднішим жебраком ніж він сам</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
